--- a/output/stock_quant_scores/LMT_balance_df.xlsx
+++ b/output/stock_quant_scores/LMT_balance_df.xlsx
@@ -1570,10 +1570,14 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>11670000000</v>
+      </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>5818000000</v>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -1581,21 +1585,29 @@
       <c r="N6" t="n">
         <v>23000000</v>
       </c>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>10959000000</v>
+      </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
+      <c r="R6" t="n">
+        <v>21600000000</v>
+      </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>39914000000</v>
+      </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>13997000000</v>
+      </c>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1609,7 +1621,9 @@
         <v>3163000000</v>
       </c>
       <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
+      <c r="AO6" t="n">
+        <v>50873000000</v>
+      </c>
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr"/>
@@ -1625,9 +1639,13 @@
       <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
+      <c r="BE6" t="n">
+        <v>19815000000</v>
+      </c>
       <c r="BF6" t="inlineStr"/>
-      <c r="BG6" t="inlineStr"/>
+      <c r="BG6" t="n">
+        <v>2981000000</v>
+      </c>
       <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr"/>
       <c r="BJ6" t="inlineStr"/>
@@ -1635,7 +1653,9 @@
       <c r="BL6" t="inlineStr"/>
       <c r="BM6" t="inlineStr"/>
       <c r="BN6" t="inlineStr"/>
-      <c r="BO6" t="inlineStr"/>
+      <c r="BO6" t="n">
+        <v>3604000000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
